--- a/data/yandex-business-price-list.xlsx
+++ b/data/yandex-business-price-list.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -888,6 +888,430 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Автоматизация</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Автоматизация отдела продаж</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sales-department-automation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Автоматизация отдела продаж: сбор заявок из сайта, мессенджеров и телефонии в одну точку, ИИ-квалификация лидов, автозадачи и follow-up, скоринг сделок по переписке, отчёт по конверсии этапов и дисциплине CRM. Работаем поверх amoCRM или Битрикс24. Срок: 3–4 недели. Москва и удалённо.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Автоматизация отдела продаж: квалификация заявок, автоматический follow-up, контроль воронки и работы менеджеров.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>450000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/for-sales-director</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/stock/offers/land-automation-sales-department.jpg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Автоматизация</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Анализ звонков отдела продаж</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>speech-analytics-sales</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Анализ звонков отдела продаж: транскрибация 100 процентов разговоров, проверка соблюдения этапов и скрипта, работа с возражениями, фиксация договорённостей и сроков, причины отказов и сводка по каждому менеджеру. Вместо выборочного прослушивания — полная картина качества разговоров. Срок: 2–3 недели. Москва и удалённо.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Речевая аналитика: транскрибация всех звонков, проверка по чек-листу скрипта, причины отказов, сводка руководителю.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>350000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/automation/speech-analytics-sales</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/stock/offers/land-automation-speech-analytics-sales.jpg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Автоматизация</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Автоматизация документооборота</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>document-flow-automation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Автоматизация документооборота: приём документов из почты, сканера, мессенджеров и ЭДО, маршруты согласования с ролями, сроками и эскалацией, автоматическая регистрация договоров, счетов и актов, журнал операций и контроль просроченных согласований. Срок: 3–4 недели. Москва и удалённо.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Автоматизация документооборота компании: маршруты согласования, договоры, счета и акты, журнал операций и сроки.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>450000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/for-coo</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/stock/offers/land-automation-invoice-processing.jpg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Автоматизация</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Распознавание документов и ввод в 1С</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ocr-1c-input</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Распознавание первичных документов: извлечение реквизитов, сумм и номенклатуры из счетов, актов, УПД и накладных, сопоставление со справочниками контрагентов и товаров, автоматическая запись в 1С. Спорные документы уходят на проверку с подсветкой сомнительных полей. Срок: 2–3 недели. Москва и удалённо.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Распознавание счетов, актов, УПД и накладных с автоматическим вводом данных в 1С без ручного набора.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>350000</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/services/ocr</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/stock/offers/ocr.jpg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CRM и интеграции</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Интеграция CRM и 1С</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>crm-1c-integration</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Интеграция CRM и 1С: обмен сделками, счетами, оплатами, контрагентами и складскими остатками, идемпотентные обмены без дублей, повторные попытки при сбое, журнал операций и мониторинг. Убирает двойной ввод одних и тех же данных менеджерами и бухгалтерией. Срок: 2–4 недели. Москва и удалённо.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Двусторонний обмен между CRM и 1С: сделки, счета, оплаты и склад без двойного ввода данных.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/integrations/crm-1c-automation</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/stock/offers/land-integrations-crm-1c-automation.jpg</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Корпоративный ИИ</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Приватный ИИ в закрытом контуре</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>private-ai-onpremise</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Приватный ИИ в закрытом контуре: развёртывание открытой LLM на вашем оборудовании, в российском облаке или гибриде, разграничение доступа по ролям и документам, аудит запросов и ответов, метрики и алерты, передача инфраструктуры как кода вашей команде. Подходит компаниям, которым нельзя отправлять данные во внешние сервисы. Срок: 4–8 недель. Москва и удалённо.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Локальная LLM on-premise или в российском облаке: без передачи данных наружу, права доступа и аудит запросов.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/secure-ai</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/stock/offers/secure-private-ai-cloud.jpg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CRM и интеграции</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Внедрение Битрикс24 под ключ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bitrix24-implementation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Внедрение Битрикс24 под ключ: настройка воронок и стадий, роботы и бизнес-процессы, права доступа, подключение сайта, мессенджеров и телефонии, обмен с 1С, перенос данных из текущей системы, обучение сотрудников и регламент работы в CRM. Срок: 2–4 недели. Москва и удалённо.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Внедрение Битрикс24 под ключ: воронки, роботы, права, интеграции с 1С, телефонией и сайтом, обучение команды.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://bitrix.bober-systems.ru</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/stock/offers/land-integrations-bitrix24-implementation.jpg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CRM и интеграции</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Внедрение amoCRM под ключ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>amocrm-implementation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Внедрение amoCRM под ключ: проектирование воронки и полей, автоматические задачи и триггеры, подключение мессенджеров, форм сайта и телефонии, обмен данными с 1С, перенос базы клиентов, обучение менеджеров и проверка дисциплины заполнения. Срок: 2–3 недели. Москва и удалённо.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Внедрение amoCRM под ключ: воронка, поля, автоматизация задач, мессенджеры и телефония, обмен с 1С.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://amocrm.bober-systems.ru</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.bober-systems.ru/stock/offers/amocrm-implementation.jpg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
